--- a/gstdatabase/GSTR-3B-2022-2023.xlsx
+++ b/gstdatabase/GSTR-3B-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A121C3-5667-41CF-984C-90A37B780D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66288CC8-39D5-4B51-B941-471AF61F8568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1531,14 +1531,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>32206</v>
+        <v>32207</v>
       </c>
       <c r="BI10" s="8">
-        <v>117482</v>
+        <v>117483</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99931100771501236</v>
+        <v>0.99931951379260486</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1556,14 +1556,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>7531</v>
+        <v>7533</v>
       </c>
       <c r="F11" s="22">
-        <v>43243</v>
+        <v>43245</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.97561140691273351</v>
+        <v>0.97565652919411605</v>
       </c>
       <c r="H11" s="9">
         <v>45199</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J47" si="2">K11-I11</f>
-        <v>9556</v>
+        <v>9558</v>
       </c>
       <c r="K11" s="22">
-        <v>44036</v>
+        <v>44038</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L47" si="3">K11/H11</f>
-        <v>0.97426934224208506</v>
+        <v>0.97431359100865067</v>
       </c>
       <c r="M11" s="4">
         <v>98966</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>17699</v>
+        <v>17702</v>
       </c>
       <c r="P11" s="8">
-        <v>96227</v>
+        <v>96230</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.97232382838550613</v>
+        <v>0.97235414182648583</v>
       </c>
       <c r="R11" s="9">
         <v>44504</v>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>8459</v>
+        <v>8462</v>
       </c>
       <c r="U11" s="8">
-        <v>43148</v>
+        <v>43151</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.96953082868955598</v>
+        <v>0.96959823836059678</v>
       </c>
       <c r="W11" s="9">
         <v>45023</v>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y47" si="8">Z11-X11</f>
-        <v>9427</v>
+        <v>9430</v>
       </c>
       <c r="Z11" s="22">
-        <v>43807</v>
+        <v>43810</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA47" si="9">Z11/W11</f>
-        <v>0.97299158208027003</v>
+        <v>0.97305821469026943</v>
       </c>
       <c r="AB11" s="9">
         <v>99888</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>20293</v>
+        <v>20298</v>
       </c>
       <c r="AE11" s="8">
-        <v>97415</v>
+        <v>97420</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.97524227134390518</v>
+        <v>0.97529232740669547</v>
       </c>
       <c r="AG11" s="9">
         <v>44744</v>
@@ -1658,14 +1658,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>8865</v>
+        <v>8868</v>
       </c>
       <c r="AJ11" s="22">
-        <v>43369</v>
+        <v>43372</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.96926962274271411</v>
+        <v>0.96933667083854813</v>
       </c>
       <c r="AL11" s="9">
         <v>45303</v>
@@ -1675,14 +1675,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN48" si="14">AO11-AM11</f>
-        <v>7703</v>
+        <v>7707</v>
       </c>
       <c r="AO11" s="22">
-        <v>43889</v>
+        <v>43893</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP48" si="15">AO11/AL11</f>
-        <v>0.96878793898858795</v>
+        <v>0.96887623336202899</v>
       </c>
       <c r="AQ11" s="15">
         <v>100769</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>14776</v>
+        <v>14779</v>
       </c>
       <c r="AT11" s="8">
-        <v>98358</v>
+        <v>98361</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.97607399100913972</v>
+        <v>0.97610376206968408</v>
       </c>
       <c r="AV11" s="9">
         <v>46153</v>
@@ -1709,14 +1709,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>7692</v>
+        <v>7695</v>
       </c>
       <c r="AY11" s="22">
-        <v>43747</v>
+        <v>43750</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.94786904426581153</v>
+        <v>0.94793404545750004</v>
       </c>
       <c r="BA11" s="9">
         <v>44735</v>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>7802</v>
+        <v>7805</v>
       </c>
       <c r="BD11" s="8">
-        <v>44767</v>
+        <v>44770</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>1.0007153235721471</v>
+        <v>1.0007823851570359</v>
       </c>
       <c r="BF11" s="9">
         <v>99991</v>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>21626</v>
+        <v>21629</v>
       </c>
       <c r="BI11" s="8">
-        <v>100719</v>
+        <v>100722</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>1.0072806552589733</v>
+        <v>1.0073106579592164</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1768,14 +1768,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>19985</v>
+        <v>19989</v>
       </c>
       <c r="F12" s="22">
-        <v>155775</v>
+        <v>155779</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.94491556267287813</v>
+        <v>0.94493982627262585</v>
       </c>
       <c r="H12" s="9">
         <v>167213</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>24934</v>
+        <v>24938</v>
       </c>
       <c r="K12" s="22">
-        <v>158989</v>
+        <v>158993</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.9508172211490733</v>
+        <v>0.95084114273411757</v>
       </c>
       <c r="M12" s="4">
         <v>342449</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>51793</v>
+        <v>51797</v>
       </c>
       <c r="P12" s="8">
-        <v>327300</v>
+        <v>327304</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.95576275591401927</v>
+        <v>0.95577443648543292</v>
       </c>
       <c r="R12" s="9">
         <v>167538</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>23861</v>
+        <v>23865</v>
       </c>
       <c r="U12" s="8">
-        <v>158029</v>
+        <v>158033</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.94324272702312306</v>
+        <v>0.94326660220367919</v>
       </c>
       <c r="W12" s="9">
         <v>169859</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>27064</v>
+        <v>27068</v>
       </c>
       <c r="Z12" s="22">
-        <v>160587</v>
+        <v>160591</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.94541354888466311</v>
+        <v>0.94543709782819874</v>
       </c>
       <c r="AB12" s="9">
         <v>346997</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>64282</v>
+        <v>64286</v>
       </c>
       <c r="AE12" s="8">
-        <v>331749</v>
+        <v>331753</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.95605725697916699</v>
+        <v>0.9560687844563498</v>
       </c>
       <c r="AG12" s="9">
         <v>170493</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>26913</v>
+        <v>26918</v>
       </c>
       <c r="AJ12" s="22">
-        <v>160381</v>
+        <v>160386</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.94068964708228486</v>
+        <v>0.94071897379951086</v>
       </c>
       <c r="AL12" s="9">
         <v>172338</v>
@@ -1887,14 +1887,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>23342</v>
+        <v>23346</v>
       </c>
       <c r="AO12" s="22">
-        <v>162781</v>
+        <v>162785</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.94454502199166757</v>
+        <v>0.94456823219487285</v>
       </c>
       <c r="AQ12" s="15">
         <v>350104</v>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>43755</v>
+        <v>43760</v>
       </c>
       <c r="AT12" s="8">
-        <v>335249</v>
+        <v>335254</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.95756975070264838</v>
+        <v>0.95758403217329713</v>
       </c>
       <c r="AV12" s="9">
         <v>177002</v>
@@ -1921,14 +1921,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>22978</v>
+        <v>22982</v>
       </c>
       <c r="AY12" s="22">
-        <v>162388</v>
+        <v>162392</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.91743596117557991</v>
+        <v>0.9174585597902849</v>
       </c>
       <c r="BA12" s="9">
         <v>166689</v>
@@ -1938,14 +1938,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>28216</v>
+        <v>28220</v>
       </c>
       <c r="BD12" s="8">
-        <v>164573</v>
+        <v>164577</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98730570103606119</v>
+        <v>0.98732969782049207</v>
       </c>
       <c r="BF12" s="9">
         <v>341156</v>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>69384</v>
+        <v>69389</v>
       </c>
       <c r="BI12" s="8">
-        <v>339918</v>
+        <v>339923</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99637116158003958</v>
+        <v>0.99638581763181655</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>15677</v>
+        <v>15678</v>
       </c>
       <c r="F14" s="22">
-        <v>78893</v>
+        <v>78894</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.95281400966183571</v>
+        <v>0.95282608695652171</v>
       </c>
       <c r="H14" s="9">
         <v>84757</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18869</v>
+        <v>18870</v>
       </c>
       <c r="K14" s="22">
-        <v>80626</v>
+        <v>80627</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.95126066283610788</v>
+        <v>0.95127246127163534</v>
       </c>
       <c r="M14" s="4">
         <v>154914</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31311</v>
+        <v>31312</v>
       </c>
       <c r="P14" s="8">
-        <v>147545</v>
+        <v>147546</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.9524316717662703</v>
+        <v>0.95243812696076535</v>
       </c>
       <c r="R14" s="9">
         <v>85475</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18034</v>
+        <v>18035</v>
       </c>
       <c r="U14" s="8">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.94031003217315001</v>
+        <v>0.94032173150043874</v>
       </c>
       <c r="W14" s="9">
         <v>86445</v>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17700</v>
+        <v>17701</v>
       </c>
       <c r="BD14" s="8">
-        <v>85369</v>
+        <v>85370</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.99014138414966535</v>
+        <v>0.99015298252125405</v>
       </c>
       <c r="BF14" s="9">
         <v>155639</v>
@@ -2379,14 +2379,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>40059</v>
+        <v>40060</v>
       </c>
       <c r="BI14" s="8">
-        <v>154746</v>
+        <v>154747</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99426236354641184</v>
+        <v>0.99426878867121993</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>61339</v>
+        <v>61340</v>
       </c>
       <c r="F16" s="22">
-        <v>393552</v>
+        <v>393553</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.95922316845486766</v>
+        <v>0.959225605802838</v>
       </c>
       <c r="H16" s="9">
         <v>416018</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74126</v>
+        <v>74127</v>
       </c>
       <c r="K16" s="22">
-        <v>400766</v>
+        <v>400767</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.96333812479267722</v>
+        <v>0.96334052853482299</v>
       </c>
       <c r="M16" s="4">
         <v>750813</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>121086</v>
+        <v>121090</v>
       </c>
       <c r="P16" s="8">
-        <v>719552</v>
+        <v>719556</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.95836380030713375</v>
+        <v>0.95836912786539397</v>
       </c>
       <c r="R16" s="9">
         <v>419109</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>73016</v>
+        <v>73017</v>
       </c>
       <c r="U16" s="8">
-        <v>401899</v>
+        <v>401900</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.95893669665886438</v>
+        <v>0.95893908267300387</v>
       </c>
       <c r="W16" s="9">
         <v>423539</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73348</v>
+        <v>73349</v>
       </c>
       <c r="Z16" s="22">
-        <v>407303</v>
+        <v>407304</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.96166586784215857</v>
+        <v>0.96166822889981796</v>
       </c>
       <c r="AB16" s="9">
         <v>762171</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>150579</v>
+        <v>150583</v>
       </c>
       <c r="AE16" s="8">
-        <v>731071</v>
+        <v>731075</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.95919550861945679</v>
+        <v>0.95920075678555072</v>
       </c>
       <c r="AG16" s="9">
         <v>429452</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79992</v>
+        <v>79994</v>
       </c>
       <c r="AJ16" s="22">
-        <v>411536</v>
+        <v>411538</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.95828171716513133</v>
+        <v>0.95828637426301422</v>
       </c>
       <c r="AL16" s="9">
         <v>434676</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70950</v>
+        <v>70954</v>
       </c>
       <c r="AO16" s="22">
-        <v>417049</v>
+        <v>417053</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.95944795663896787</v>
+        <v>0.9594571588953611</v>
       </c>
       <c r="AQ16" s="15">
         <v>772632</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>110182</v>
+        <v>110190</v>
       </c>
       <c r="AT16" s="8">
-        <v>741487</v>
+        <v>741495</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.95968973586390416</v>
+        <v>0.95970009008169477</v>
       </c>
       <c r="AV16" s="9">
         <v>448203</v>
@@ -2769,14 +2769,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69550</v>
+        <v>69555</v>
       </c>
       <c r="AY16" s="22">
-        <v>420006</v>
+        <v>420011</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.93708877450619477</v>
+        <v>0.93709993016557225</v>
       </c>
       <c r="BA16" s="9">
         <v>429555</v>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70943</v>
+        <v>70948</v>
       </c>
       <c r="BD16" s="8">
-        <v>424815</v>
+        <v>424820</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98896532458008868</v>
+        <v>0.98897696453306327</v>
       </c>
       <c r="BF16" s="9">
         <v>753579</v>
@@ -2803,14 +2803,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>147992</v>
+        <v>148001</v>
       </c>
       <c r="BI16" s="8">
-        <v>751194</v>
+        <v>751203</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99683510288901367</v>
+        <v>0.99684704589697959</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>51284</v>
+        <v>51286</v>
       </c>
       <c r="F17" s="22">
-        <v>277336</v>
+        <v>277338</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.98043277677810736</v>
+        <v>0.98043984713880183</v>
       </c>
       <c r="H17" s="9">
         <v>290053</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>59548</v>
+        <v>59551</v>
       </c>
       <c r="K17" s="22">
-        <v>284835</v>
+        <v>284838</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.9820101843456196</v>
+        <v>0.98202052728294487</v>
       </c>
       <c r="M17" s="4">
         <v>666005</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>128129</v>
+        <v>128133</v>
       </c>
       <c r="P17" s="8">
-        <v>645993</v>
+        <v>645997</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.96995217753620466</v>
+        <v>0.96995818349712093</v>
       </c>
       <c r="R17" s="9">
         <v>287981</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55282</v>
+        <v>55285</v>
       </c>
       <c r="U17" s="8">
-        <v>280827</v>
+        <v>280830</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.97515808334577625</v>
+        <v>0.97516850069969896</v>
       </c>
       <c r="W17" s="9">
         <v>293004</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>60477</v>
+        <v>60480</v>
       </c>
       <c r="Z17" s="22">
-        <v>286664</v>
+        <v>286667</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97836207014238719</v>
+        <v>0.97837230891045857</v>
       </c>
       <c r="AB17" s="9">
         <v>677720</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145686</v>
+        <v>145689</v>
       </c>
       <c r="AE17" s="8">
-        <v>658947</v>
+        <v>658950</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.97229976981644339</v>
+        <v>0.97230419642330168</v>
       </c>
       <c r="AG17" s="9">
         <v>295677</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59677</v>
+        <v>59679</v>
       </c>
       <c r="AJ17" s="22">
-        <v>288121</v>
+        <v>288123</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.9744450870375444</v>
+        <v>0.97445185117543809</v>
       </c>
       <c r="AL17" s="9">
         <v>303084</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51550</v>
+        <v>51552</v>
       </c>
       <c r="AO17" s="22">
-        <v>296058</v>
+        <v>296060</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.97681830779585854</v>
+        <v>0.97682490662654575</v>
       </c>
       <c r="AQ17" s="15">
         <v>690105</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>105810</v>
+        <v>105815</v>
       </c>
       <c r="AT17" s="8">
-        <v>672955</v>
+        <v>672960</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.97514870925438879</v>
+        <v>0.97515595452865866</v>
       </c>
       <c r="AV17" s="9">
         <v>311697</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>49019</v>
+        <v>49022</v>
       </c>
       <c r="AY17" s="22">
-        <v>294862</v>
+        <v>294865</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.94598921388399637</v>
+        <v>0.94599883861570688</v>
       </c>
       <c r="BA17" s="9">
         <v>307540</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>49217</v>
+        <v>49219</v>
       </c>
       <c r="BD17" s="8">
-        <v>301990</v>
+        <v>301992</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98195356701567271</v>
+        <v>0.98196007023476617</v>
       </c>
       <c r="BF17" s="9">
         <v>689646</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>153213</v>
+        <v>153218</v>
       </c>
       <c r="BI17" s="8">
-        <v>687233</v>
+        <v>687238</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99650110346467613</v>
+        <v>0.99650835356110234</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>141576</v>
+        <v>141578</v>
       </c>
       <c r="F18" s="22">
-        <v>822089</v>
+        <v>822091</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.978096345147347</v>
+        <v>0.97809872468616854</v>
       </c>
       <c r="H18" s="9">
         <v>861805</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>162049</v>
+        <v>162051</v>
       </c>
       <c r="K18" s="22">
-        <v>837283</v>
+        <v>837285</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.97154576731395148</v>
+        <v>0.97154808802455317</v>
       </c>
       <c r="M18" s="4">
         <v>1358945</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>245611</v>
+        <v>245613</v>
       </c>
       <c r="P18" s="8">
-        <v>1303844</v>
+        <v>1303846</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.95945310516613991</v>
+        <v>0.95945457689604807</v>
       </c>
       <c r="R18" s="9">
         <v>869959</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>158479</v>
+        <v>158481</v>
       </c>
       <c r="U18" s="8">
-        <v>839494</v>
+        <v>839496</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.96498110830510408</v>
+        <v>0.96498340726402054</v>
       </c>
       <c r="W18" s="9">
         <v>883450</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>163358</v>
+        <v>163361</v>
       </c>
       <c r="Z18" s="22">
-        <v>853937</v>
+        <v>853940</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.96659346878714136</v>
+        <v>0.96659686456505745</v>
       </c>
       <c r="AB18" s="9">
         <v>1397129</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>289657</v>
+        <v>289660</v>
       </c>
       <c r="AE18" s="8">
-        <v>1339786</v>
+        <v>1339789</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.95895654588803181</v>
+        <v>0.95895869314859261</v>
       </c>
       <c r="AG18" s="9">
         <v>899515</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>168553</v>
+        <v>168557</v>
       </c>
       <c r="AJ18" s="22">
-        <v>864930</v>
+        <v>864934</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.96155150275426204</v>
+        <v>0.96155594959505952</v>
       </c>
       <c r="AL18" s="9">
         <v>914748</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>146488</v>
+        <v>146492</v>
       </c>
       <c r="AO18" s="22">
-        <v>880814</v>
+        <v>880818</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.96290344444590203</v>
+        <v>0.96290781723491059</v>
       </c>
       <c r="AQ18" s="15">
         <v>1436617</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>219839</v>
+        <v>219841</v>
       </c>
       <c r="AT18" s="8">
-        <v>1375261</v>
+        <v>1375263</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.95729133095320462</v>
+        <v>0.95729272311270153</v>
       </c>
       <c r="AV18" s="9">
         <v>954168</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>153030</v>
+        <v>153033</v>
       </c>
       <c r="AY18" s="22">
-        <v>894817</v>
+        <v>894820</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.93779816552221407</v>
+        <v>0.93780130962262409</v>
       </c>
       <c r="BA18" s="9">
         <v>922519</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>158412</v>
+        <v>158414</v>
       </c>
       <c r="BD18" s="8">
-        <v>911456</v>
+        <v>911458</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.9880078350689796</v>
+        <v>0.98801000304600772</v>
       </c>
       <c r="BF18" s="9">
         <v>1428140</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>327770</v>
+        <v>327773</v>
       </c>
       <c r="BI18" s="8">
-        <v>1413424</v>
+        <v>1413427</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.9896956880978055</v>
+        <v>0.98969778873219716</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3252,14 +3252,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>54817</v>
+        <v>54819</v>
       </c>
       <c r="F19" s="22">
-        <v>245687</v>
+        <v>245689</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.88871485827557772</v>
+        <v>0.88872209280453751</v>
       </c>
       <c r="H19" s="9">
         <v>280982</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>89975</v>
+        <v>89977</v>
       </c>
       <c r="K19" s="22">
-        <v>250789</v>
+        <v>250791</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.89254471816699998</v>
+        <v>0.8925518360606729</v>
       </c>
       <c r="M19" s="4">
         <v>470659</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>92082</v>
+        <v>92084</v>
       </c>
       <c r="P19" s="8">
-        <v>424573</v>
+        <v>424575</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.90208197442309612</v>
+        <v>0.90208622378409842</v>
       </c>
       <c r="R19" s="9">
         <v>282327</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>55609</v>
+        <v>55611</v>
       </c>
       <c r="U19" s="8">
-        <v>249699</v>
+        <v>249701</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.88443188217917523</v>
+        <v>0.8844389661633496</v>
       </c>
       <c r="W19" s="9">
         <v>286093</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>58857</v>
+        <v>58860</v>
       </c>
       <c r="Z19" s="22">
-        <v>254770</v>
+        <v>254773</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.89051462286738925</v>
+        <v>0.89052510896806281</v>
       </c>
       <c r="AB19" s="9">
         <v>481143</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>107383</v>
+        <v>107386</v>
       </c>
       <c r="AE19" s="8">
-        <v>435537</v>
+        <v>435540</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.90521321104120811</v>
+        <v>0.90521944619375116</v>
       </c>
       <c r="AG19" s="9">
         <v>287213</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="AJ19" s="22">
-        <v>254662</v>
+        <v>254666</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.88666599353093345</v>
+        <v>0.88667992047713717</v>
       </c>
       <c r="AL19" s="9">
         <v>292666</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>53092</v>
+        <v>53096</v>
       </c>
       <c r="AO19" s="22">
-        <v>260286</v>
+        <v>260290</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.88936193476522729</v>
+        <v>0.88937560222232848</v>
       </c>
       <c r="AQ19" s="15">
         <v>495564</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>83377</v>
+        <v>83382</v>
       </c>
       <c r="AT19" s="8">
-        <v>446777</v>
+        <v>446782</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.90155257444043557</v>
+        <v>0.90156266395460527</v>
       </c>
       <c r="AV19" s="9">
         <v>310298</v>
@@ -3405,14 +3405,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>52457</v>
+        <v>52461</v>
       </c>
       <c r="AY19" s="22">
-        <v>264471</v>
+        <v>264475</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.85231293788551654</v>
+        <v>0.85232582871948903</v>
       </c>
       <c r="BA19" s="9">
         <v>280202</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>55913</v>
+        <v>55917</v>
       </c>
       <c r="BD19" s="8">
-        <v>272820</v>
+        <v>272824</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.97365472052305124</v>
+        <v>0.97366899593864431</v>
       </c>
       <c r="BF19" s="9">
         <v>473091</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>125849</v>
+        <v>125854</v>
       </c>
       <c r="BI19" s="8">
-        <v>463175</v>
+        <v>463180</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.9790399732820958</v>
+        <v>0.97905054207330089</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="AO20" s="22">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.86456717344089362</v>
+        <v>0.86472230840831521</v>
       </c>
       <c r="AQ20" s="15">
         <v>9604</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="AT20" s="8">
-        <v>8619</v>
+        <v>8620</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.89743856726364013</v>
+        <v>0.89754269054560598</v>
       </c>
       <c r="AV20" s="9">
         <v>6642</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="AY20" s="22">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.84613068352905751</v>
+        <v>0.84628124059018373</v>
       </c>
       <c r="BA20" s="9">
         <v>5628</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="BD20" s="8">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>1.0174129353233832</v>
+        <v>1.017590618336887</v>
       </c>
       <c r="BF20" s="9">
         <v>8802</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="BI20" s="8">
-        <v>8960</v>
+        <v>8961</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0179504658032266</v>
+        <v>1.0180640763462849</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3676,14 +3676,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="F21" s="22">
-        <v>8600</v>
+        <v>8601</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.81002166337006687</v>
+        <v>0.810115851935575</v>
       </c>
       <c r="H21" s="9">
         <v>10811</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="K21" s="22">
-        <v>8743</v>
+        <v>8744</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.80871334751641843</v>
+        <v>0.80880584589769677</v>
       </c>
       <c r="M21" s="4">
         <v>14133</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>3840</v>
+        <v>3841</v>
       </c>
       <c r="P21" s="8">
-        <v>11810</v>
+        <v>11811</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>0.83563291587065736</v>
+        <v>0.83570367225642117</v>
       </c>
       <c r="R21" s="9">
         <v>11019</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="U21" s="8">
-        <v>8897</v>
+        <v>8898</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>0.80742354115618475</v>
+        <v>0.80751429349305748</v>
       </c>
       <c r="W21" s="9">
         <v>11175</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="Z21" s="22">
-        <v>9095</v>
+        <v>9096</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.81387024608501124</v>
+        <v>0.81395973154362411</v>
       </c>
       <c r="AB21" s="9">
         <v>14571</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4488</v>
+        <v>4489</v>
       </c>
       <c r="AE21" s="8">
-        <v>12222</v>
+        <v>12223</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.83878937615812232</v>
+        <v>0.83885800562761648</v>
       </c>
       <c r="AG21" s="9">
         <v>11345</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3238</v>
+        <v>3240</v>
       </c>
       <c r="AJ21" s="22">
-        <v>9228</v>
+        <v>9230</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.81339797267518732</v>
+        <v>0.81357426178933456</v>
       </c>
       <c r="AL21" s="9">
         <v>11441</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3102</v>
+        <v>3105</v>
       </c>
       <c r="AO21" s="22">
-        <v>9350</v>
+        <v>9353</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.81723625557206536</v>
+        <v>0.81749847041342538</v>
       </c>
       <c r="AQ21" s="15">
         <v>14790</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4021</v>
+        <v>4024</v>
       </c>
       <c r="AT21" s="8">
-        <v>12506</v>
+        <v>12509</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.84557133198106826</v>
+        <v>0.84577417173766056</v>
       </c>
       <c r="AV21" s="9">
         <v>11740</v>
@@ -3829,14 +3829,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3230</v>
+        <v>3233</v>
       </c>
       <c r="AY21" s="22">
-        <v>9490</v>
+        <v>9493</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.80834752981260649</v>
+        <v>0.80860306643952296</v>
       </c>
       <c r="BA21" s="9">
         <v>9242</v>
@@ -3846,14 +3846,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3132</v>
+        <v>3135</v>
       </c>
       <c r="BD21" s="8">
-        <v>9585</v>
+        <v>9588</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0371131789655919</v>
+        <v>1.0374377840294309</v>
       </c>
       <c r="BF21" s="9">
         <v>12544</v>
@@ -3863,14 +3863,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5690</v>
+        <v>5692</v>
       </c>
       <c r="BI21" s="8">
-        <v>12912</v>
+        <v>12914</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0293367346938775</v>
+        <v>1.0294961734693877</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="AJ22" s="22">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.91842346471127401</v>
+        <v>0.91857622975863118</v>
       </c>
       <c r="AL22" s="9">
         <v>6648</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="AO22" s="22">
-        <v>6073</v>
+        <v>6074</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.91350782190132374</v>
+        <v>0.91365824308062571</v>
       </c>
       <c r="AQ22" s="15">
         <v>7880</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="AT22" s="8">
-        <v>7265</v>
+        <v>7266</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.92195431472081213</v>
+        <v>0.92208121827411171</v>
       </c>
       <c r="AV22" s="9">
         <v>6715</v>
@@ -4041,14 +4041,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="AY22" s="22">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.90796723752792252</v>
+        <v>0.90811615785554733</v>
       </c>
       <c r="BA22" s="9">
         <v>6117</v>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="BD22" s="8">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.0045774072257643</v>
+        <v>1.0047408860552558</v>
       </c>
       <c r="BF22" s="9">
         <v>7349</v>
@@ -4075,14 +4075,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="BI22" s="8">
-        <v>7405</v>
+        <v>7406</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.0076200843652197</v>
+        <v>1.0077561573003129</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4134,14 +4134,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="P23" s="8">
-        <v>9657</v>
+        <v>9658</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.87164906580016244</v>
+        <v>0.8717393266540302</v>
       </c>
       <c r="R23" s="9">
         <v>9156</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="U23" s="8">
-        <v>7941</v>
+        <v>7942</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.86730013106159898</v>
+        <v>0.8674093490607252</v>
       </c>
       <c r="W23" s="9">
         <v>9166</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="Z23" s="22">
-        <v>8113</v>
+        <v>8114</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.88511891773947193</v>
+        <v>0.88522801658302419</v>
       </c>
       <c r="AB23" s="9">
         <v>11322</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="AE23" s="8">
-        <v>10054</v>
+        <v>10055</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.88800565271153509</v>
+        <v>0.88809397632927045</v>
       </c>
       <c r="AG23" s="9">
         <v>9569</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="AJ23" s="22">
-        <v>8229</v>
+        <v>8230</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.85996446859650955</v>
+        <v>0.86006897272442262</v>
       </c>
       <c r="AL23" s="9">
         <v>9502</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="AO23" s="22">
-        <v>8343</v>
+        <v>8344</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.87802567880446225</v>
+        <v>0.8781309198063566</v>
       </c>
       <c r="AQ23" s="15">
         <v>11767</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="AT23" s="8">
-        <v>10347</v>
+        <v>10348</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.87932353191127732</v>
+        <v>0.87940851533950881</v>
       </c>
       <c r="AV23" s="9">
         <v>9805</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="AY23" s="22">
-        <v>8437</v>
+        <v>8438</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.86047934727180009</v>
+        <v>0.86058133605303422</v>
       </c>
       <c r="BA23" s="9">
         <v>8694</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="BD23" s="8">
-        <v>8536</v>
+        <v>8537</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.98182654704393835</v>
+        <v>0.98194156889809059</v>
       </c>
       <c r="BF23" s="9">
         <v>11229</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4621</v>
+        <v>4622</v>
       </c>
       <c r="BI23" s="8">
-        <v>10607</v>
+        <v>10608</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.94460771217383566</v>
+        <v>0.94469676729895802</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="P24" s="8">
-        <v>6057</v>
+        <v>6058</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.8352178709321566</v>
+        <v>0.83535576392719246</v>
       </c>
       <c r="R24" s="9">
         <v>6353</v>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="U24" s="8">
-        <v>5208</v>
+        <v>5209</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.81977018731308049</v>
+        <v>0.81992759326302533</v>
       </c>
       <c r="W24" s="9">
         <v>6421</v>
@@ -4380,14 +4380,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="Z24" s="22">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.82199034418314909</v>
+        <v>0.82214608316461613</v>
       </c>
       <c r="AB24" s="9">
         <v>7434</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="AE24" s="8">
-        <v>6223</v>
+        <v>6224</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.83709981167608283</v>
+        <v>0.83723432875975246</v>
       </c>
       <c r="AG24" s="9">
         <v>6545</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="AJ24" s="22">
-        <v>5337</v>
+        <v>5338</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.81543162719633311</v>
+        <v>0.81558441558441563</v>
       </c>
       <c r="AL24" s="9">
         <v>6623</v>
@@ -4431,14 +4431,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="AO24" s="22">
-        <v>5429</v>
+        <v>5430</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.81971916050128346</v>
+        <v>0.81987014947908798</v>
       </c>
       <c r="AQ24" s="15">
         <v>7610</v>
@@ -4448,14 +4448,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AT24" s="8">
-        <v>6383</v>
+        <v>6384</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.83876478318002623</v>
+        <v>0.83889618922470433</v>
       </c>
       <c r="AV24" s="9">
         <v>6365</v>
@@ -4465,14 +4465,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="AY24" s="22">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.85483110761979575</v>
+        <v>0.85498821681068338</v>
       </c>
       <c r="BA24" s="9">
         <v>5683</v>
@@ -4482,14 +4482,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="BD24" s="8">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.96533521027626257</v>
+        <v>0.96551117367587547</v>
       </c>
       <c r="BF24" s="9">
         <v>6688</v>
@@ -4499,14 +4499,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="BI24" s="8">
-        <v>6492</v>
+        <v>6493</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.97069377990430628</v>
+        <v>0.97084330143540665</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="F25" s="22">
-        <v>17485</v>
+        <v>17486</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.9213785108288981</v>
+        <v>0.92143120619697527</v>
       </c>
       <c r="H25" s="9">
         <v>19277</v>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="K25" s="22">
-        <v>17703</v>
+        <v>17704</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.91834829070913526</v>
+        <v>0.91840016600093377</v>
       </c>
       <c r="M25" s="4">
         <v>26614</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4373</v>
+        <v>4374</v>
       </c>
       <c r="P25" s="8">
-        <v>24778</v>
+        <v>24779</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.93101375216051707</v>
+        <v>0.93105132636957988</v>
       </c>
       <c r="R25" s="9">
         <v>19402</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="U25" s="8">
-        <v>17851</v>
+        <v>17852</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.92005978765075769</v>
+        <v>0.92011132872899704</v>
       </c>
       <c r="W25" s="9">
         <v>19474</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3578</v>
+        <v>3579</v>
       </c>
       <c r="Z25" s="22">
-        <v>18049</v>
+        <v>18050</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.92682551093766052</v>
+        <v>0.92687686145630066</v>
       </c>
       <c r="AB25" s="9">
         <v>27081</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="AE25" s="8">
-        <v>25184</v>
+        <v>25185</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.92995088807651116</v>
+        <v>0.92998781433477351</v>
       </c>
       <c r="AG25" s="9">
         <v>19543</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>3609</v>
+        <v>3610</v>
       </c>
       <c r="AJ25" s="22">
-        <v>18113</v>
+        <v>18114</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.92682802026300981</v>
+        <v>0.92687918947960912</v>
       </c>
       <c r="AL25" s="9">
         <v>19594</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="AO25" s="22">
-        <v>18304</v>
+        <v>18305</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.93416351944472797</v>
+        <v>0.93421455547616616</v>
       </c>
       <c r="AQ25" s="15">
         <v>26830</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>4458</v>
+        <v>4459</v>
       </c>
       <c r="AT25" s="8">
-        <v>25424</v>
+        <v>25425</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.94759597465523671</v>
+        <v>0.94763324636600821</v>
       </c>
       <c r="AV25" s="9">
         <v>19719</v>
@@ -4677,14 +4677,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="AY25" s="22">
-        <v>18390</v>
+        <v>18391</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.93260307317815305</v>
+        <v>0.93265378568892943</v>
       </c>
       <c r="BA25" s="9">
         <v>18241</v>
@@ -4694,14 +4694,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="BD25" s="8">
-        <v>18402</v>
+        <v>18403</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>1.0088262704895565</v>
+        <v>1.0088810920453923</v>
       </c>
       <c r="BF25" s="9">
         <v>25358</v>
@@ -4711,14 +4711,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7386</v>
+        <v>7387</v>
       </c>
       <c r="BI25" s="8">
-        <v>25659</v>
+        <v>25660</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0118700212950549</v>
+        <v>1.0119094565817492</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3349</v>
+        <v>3351</v>
       </c>
       <c r="F26" s="22">
-        <v>12923</v>
+        <v>12925</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.80728385807096448</v>
+        <v>0.80740879560219891</v>
       </c>
       <c r="H26" s="9">
         <v>16365</v>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3590</v>
+        <v>3592</v>
       </c>
       <c r="K26" s="22">
-        <v>13397</v>
+        <v>13399</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.81863733577757414</v>
+        <v>0.81875954781545979</v>
       </c>
       <c r="M26" s="4">
         <v>27510</v>
@@ -4770,14 +4770,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5027</v>
+        <v>5031</v>
       </c>
       <c r="P26" s="8">
-        <v>24140</v>
+        <v>24144</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.87749909123954928</v>
+        <v>0.87764449291166846</v>
       </c>
       <c r="R26" s="9">
         <v>16566</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3647</v>
+        <v>3650</v>
       </c>
       <c r="U26" s="8">
-        <v>13601</v>
+        <v>13604</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.82101895448508999</v>
+        <v>0.82120004829168181</v>
       </c>
       <c r="W26" s="9">
         <v>16728</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3631</v>
+        <v>3634</v>
       </c>
       <c r="Z26" s="22">
-        <v>13812</v>
+        <v>13815</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.82568149210903874</v>
+        <v>0.82586083213773309</v>
       </c>
       <c r="AB26" s="9">
         <v>28240</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5973</v>
+        <v>5978</v>
       </c>
       <c r="AE26" s="8">
-        <v>24946</v>
+        <v>24951</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.88335694050991498</v>
+        <v>0.88353399433427759</v>
       </c>
       <c r="AG26" s="9">
         <v>16538</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3548</v>
+        <v>3551</v>
       </c>
       <c r="AJ26" s="22">
-        <v>13501</v>
+        <v>13504</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.81636231708791873</v>
+        <v>0.81654371749909305</v>
       </c>
       <c r="AL26" s="9">
         <v>16671</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="AO26" s="22">
-        <v>13615</v>
+        <v>13618</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.81668766120808589</v>
+        <v>0.81686761442025069</v>
       </c>
       <c r="AQ26" s="15">
         <v>28406</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5538</v>
+        <v>5543</v>
       </c>
       <c r="AT26" s="8">
-        <v>25082</v>
+        <v>25087</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.882982468492572</v>
+        <v>0.88315848764345561</v>
       </c>
       <c r="AV26" s="9">
         <v>16717</v>
@@ -4889,14 +4889,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="AY26" s="22">
-        <v>13310</v>
+        <v>13314</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.79619548962134357</v>
+        <v>0.79643476700364901</v>
       </c>
       <c r="BA26" s="9">
         <v>13719</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3280</v>
+        <v>3284</v>
       </c>
       <c r="BD26" s="8">
-        <v>13418</v>
+        <v>13422</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97805962533712365</v>
+        <v>0.97835119177782637</v>
       </c>
       <c r="BF26" s="9">
         <v>25779</v>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6623</v>
+        <v>6629</v>
       </c>
       <c r="BI26" s="8">
-        <v>25121</v>
+        <v>25127</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.97447534815159631</v>
+        <v>0.97470809573684003</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>32561</v>
+        <v>32565</v>
       </c>
       <c r="F27" s="22">
-        <v>112763</v>
+        <v>112767</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.95153831873491634</v>
+        <v>0.95157207230013674</v>
       </c>
       <c r="H27" s="9">
         <v>121212</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>34901</v>
+        <v>34906</v>
       </c>
       <c r="K27" s="22">
-        <v>114783</v>
+        <v>114788</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.94696069696069696</v>
+        <v>0.94700194700194695</v>
       </c>
       <c r="M27" s="4">
         <v>178312</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>46497</v>
+        <v>46503</v>
       </c>
       <c r="P27" s="8">
-        <v>168585</v>
+        <v>168591</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.94544954910493961</v>
+        <v>0.94548319799003988</v>
       </c>
       <c r="R27" s="9">
         <v>121489</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32069</v>
+        <v>32075</v>
       </c>
       <c r="U27" s="8">
-        <v>115003</v>
+        <v>115009</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.94661245050992271</v>
+        <v>0.9466618376972401</v>
       </c>
       <c r="W27" s="9">
         <v>123451</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>35420</v>
+        <v>35426</v>
       </c>
       <c r="Z27" s="22">
-        <v>116905</v>
+        <v>116911</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.94697491312342552</v>
+        <v>0.94702351540287244</v>
       </c>
       <c r="AB27" s="9">
         <v>182601</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>53474</v>
+        <v>53481</v>
       </c>
       <c r="AE27" s="8">
-        <v>173171</v>
+        <v>173178</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.94835734744059452</v>
+        <v>0.94839568238947214</v>
       </c>
       <c r="AG27" s="9">
         <v>124689</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33831</v>
+        <v>33838</v>
       </c>
       <c r="AJ27" s="22">
-        <v>117395</v>
+        <v>117402</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.94150245811579214</v>
+        <v>0.9415585977913048</v>
       </c>
       <c r="AL27" s="9">
         <v>127177</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31122</v>
+        <v>31130</v>
       </c>
       <c r="AO27" s="22">
-        <v>119332</v>
+        <v>119340</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.93831431784049002</v>
+        <v>0.93837722229648446</v>
       </c>
       <c r="AQ27" s="15">
         <v>185152</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44039</v>
+        <v>44050</v>
       </c>
       <c r="AT27" s="8">
-        <v>176399</v>
+        <v>176410</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.95272532837884549</v>
+        <v>0.95278473902523331</v>
       </c>
       <c r="AV27" s="9">
         <v>127611</v>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30410</v>
+        <v>30419</v>
       </c>
       <c r="AY27" s="22">
-        <v>119210</v>
+        <v>119219</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.93416711725478208</v>
+        <v>0.93423764409024301</v>
       </c>
       <c r="BA27" s="9">
         <v>122070</v>
@@ -5118,14 +5118,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31288</v>
+        <v>31297</v>
       </c>
       <c r="BD27" s="8">
-        <v>120879</v>
+        <v>120888</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.99024330302285579</v>
+        <v>0.99031703121159986</v>
       </c>
       <c r="BF27" s="9">
         <v>180737</v>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65936</v>
+        <v>65948</v>
       </c>
       <c r="BI27" s="8">
-        <v>179339</v>
+        <v>179351</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99226500384536642</v>
+        <v>0.99233139866214448</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5194,14 +5194,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>99957</v>
+        <v>99958</v>
       </c>
       <c r="P28" s="8">
-        <v>609216</v>
+        <v>609217</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.96154550333028188</v>
+        <v>0.96154708166293124</v>
       </c>
       <c r="R28" s="9">
         <v>370844</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>116203</v>
+        <v>116204</v>
       </c>
       <c r="AE28" s="8">
-        <v>620730</v>
+        <v>620731</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.96513132117246825</v>
+        <v>0.96513287600519937</v>
       </c>
       <c r="AG28" s="9">
         <v>378725</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>88407</v>
+        <v>88408</v>
       </c>
       <c r="AT28" s="8">
-        <v>628968</v>
+        <v>628969</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.96314887609048849</v>
+        <v>0.96315040740667013</v>
       </c>
       <c r="AV28" s="9">
         <v>393378</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>133757</v>
+        <v>133758</v>
       </c>
       <c r="BI28" s="8">
-        <v>639632</v>
+        <v>639633</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99396749721062794</v>
+        <v>0.99396905117837375</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>22289</v>
+        <v>22290</v>
       </c>
       <c r="F29" s="22">
-        <v>115938</v>
+        <v>115939</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.96167819638680141</v>
+        <v>0.96168649114948823</v>
       </c>
       <c r="H29" s="9">
         <v>121339</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>25248</v>
+        <v>25249</v>
       </c>
       <c r="K29" s="22">
-        <v>116956</v>
+        <v>116957</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.96387806064002501</v>
+        <v>0.96388630201336756</v>
       </c>
       <c r="M29" s="4">
         <v>168897</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30928</v>
+        <v>30931</v>
       </c>
       <c r="P29" s="8">
-        <v>162692</v>
+        <v>162695</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.96326163282947597</v>
+        <v>0.9632793951343126</v>
       </c>
       <c r="R29" s="9">
         <v>122532</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>37474</v>
+        <v>37476</v>
       </c>
       <c r="AE29" s="8">
-        <v>166138</v>
+        <v>166140</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.96215389783000238</v>
+        <v>0.96216548041674144</v>
       </c>
       <c r="AG29" s="9">
         <v>125793</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>28297</v>
+        <v>28299</v>
       </c>
       <c r="AT29" s="8">
-        <v>169053</v>
+        <v>169055</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.96143521730723291</v>
+        <v>0.96144659167169033</v>
       </c>
       <c r="AV29" s="9">
         <v>130198</v>
@@ -5525,14 +5525,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22060</v>
+        <v>22061</v>
       </c>
       <c r="AY29" s="22">
-        <v>123787</v>
+        <v>123788</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.95075961228283079</v>
+        <v>0.95076729289236395</v>
       </c>
       <c r="BA29" s="9">
         <v>127545</v>
@@ -5542,14 +5542,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>22791</v>
+        <v>22792</v>
       </c>
       <c r="BD29" s="8">
-        <v>125578</v>
+        <v>125579</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98457799208122621</v>
+        <v>0.98458583245129172</v>
       </c>
       <c r="BF29" s="9">
         <v>174166</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>42590</v>
+        <v>42593</v>
       </c>
       <c r="BI29" s="8">
-        <v>172596</v>
+        <v>172599</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99098561142817776</v>
+        <v>0.99100283637449327</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5830,14 +5830,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>36850</v>
+        <v>36852</v>
       </c>
       <c r="P31" s="8">
-        <v>126934</v>
+        <v>126936</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.96050789615067389</v>
+        <v>0.96052303012417428</v>
       </c>
       <c r="R31" s="9">
         <v>74474</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20044</v>
+        <v>20045</v>
       </c>
       <c r="U31" s="8">
-        <v>71230</v>
+        <v>71231</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>0.95644117410102858</v>
+        <v>0.95645460160592954</v>
       </c>
       <c r="W31" s="9">
         <v>75697</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>22608</v>
+        <v>22609</v>
       </c>
       <c r="Z31" s="22">
-        <v>72501</v>
+        <v>72502</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.95777904012048032</v>
+        <v>0.9577922506836466</v>
       </c>
       <c r="AB31" s="9">
         <v>133809</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>38790</v>
+        <v>38792</v>
       </c>
       <c r="AE31" s="8">
-        <v>129181</v>
+        <v>129183</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.96541338773924024</v>
+        <v>0.96542833441696752</v>
       </c>
       <c r="AG31" s="9">
         <v>75434</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>32619</v>
+        <v>32621</v>
       </c>
       <c r="AT31" s="8">
-        <v>131036</v>
+        <v>131038</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.96672716273442227</v>
+        <v>0.9667419178728992</v>
       </c>
       <c r="AV31" s="9">
         <v>78435</v>
@@ -5949,14 +5949,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18418</v>
+        <v>18420</v>
       </c>
       <c r="AY31" s="22">
-        <v>73387</v>
+        <v>73389</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>0.93564097660483203</v>
+        <v>0.93566647542551162</v>
       </c>
       <c r="BA31" s="9">
         <v>76166</v>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>19444</v>
+        <v>19446</v>
       </c>
       <c r="BD31" s="8">
-        <v>74507</v>
+        <v>74509</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.97821862773415957</v>
+        <v>0.97824488616968197</v>
       </c>
       <c r="BF31" s="9">
         <v>132970</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>49531</v>
+        <v>49532</v>
       </c>
       <c r="BI31" s="8">
-        <v>132953</v>
+        <v>132954</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.9998721516131458</v>
+        <v>0.9998796721064902</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6008,14 +6008,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>38782</v>
+        <v>38783</v>
       </c>
       <c r="F32" s="22">
-        <v>188996</v>
+        <v>188997</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.98436442046271311</v>
+        <v>0.98436962885030055</v>
       </c>
       <c r="H32" s="9">
         <v>196288</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46873</v>
+        <v>46874</v>
       </c>
       <c r="K32" s="22">
-        <v>192873</v>
+        <v>192874</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98260209488099115</v>
+        <v>0.98260718943593084</v>
       </c>
       <c r="M32" s="4">
         <v>418497</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>94443</v>
+        <v>94444</v>
       </c>
       <c r="P32" s="8">
-        <v>409073</v>
+        <v>409074</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.97748132005725252</v>
+        <v>0.97748370956064201</v>
       </c>
       <c r="R32" s="9">
         <v>194320</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>42841</v>
+        <v>42842</v>
       </c>
       <c r="U32" s="8">
-        <v>190347</v>
+        <v>190348</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.97955434335117331</v>
+        <v>0.97955948950185256</v>
       </c>
       <c r="W32" s="9">
         <v>198209</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>47433</v>
+        <v>47434</v>
       </c>
       <c r="Z32" s="22">
-        <v>194356</v>
+        <v>194357</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98056092306605658</v>
+        <v>0.98056596824563969</v>
       </c>
       <c r="AB32" s="9">
         <v>426405</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>98667</v>
+        <v>98668</v>
       </c>
       <c r="AE32" s="8">
-        <v>418381</v>
+        <v>418382</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98118220940185974</v>
+        <v>0.98118455459011977</v>
       </c>
       <c r="AG32" s="9">
         <v>199136</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>44768</v>
+        <v>44770</v>
       </c>
       <c r="AJ32" s="22">
-        <v>195381</v>
+        <v>195383</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.98114354009320259</v>
+        <v>0.9811535834806363</v>
       </c>
       <c r="AL32" s="9">
         <v>204506</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>38345</v>
+        <v>38347</v>
       </c>
       <c r="AO32" s="22">
-        <v>199950</v>
+        <v>199952</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.9777219250290945</v>
+        <v>0.97773170469326087</v>
       </c>
       <c r="AQ32" s="15">
         <v>435626</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>82521</v>
+        <v>82523</v>
       </c>
       <c r="AT32" s="8">
-        <v>426567</v>
+        <v>426569</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.97920463884157516</v>
+        <v>0.97920922993577064</v>
       </c>
       <c r="AV32" s="9">
         <v>208760</v>
@@ -6161,14 +6161,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>38569</v>
+        <v>38571</v>
       </c>
       <c r="AY32" s="22">
-        <v>199583</v>
+        <v>199585</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.95604042920099641</v>
+        <v>0.95605000958037933</v>
       </c>
       <c r="BA32" s="9">
         <v>206539</v>
@@ -6178,14 +6178,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>40479</v>
+        <v>40481</v>
       </c>
       <c r="BD32" s="8">
-        <v>203800</v>
+        <v>203802</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98673858205956255</v>
+        <v>0.98674826546076044</v>
       </c>
       <c r="BF32" s="9">
         <v>435831</v>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>128642</v>
+        <v>128644</v>
       </c>
       <c r="BI32" s="8">
-        <v>435174</v>
+        <v>435176</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99849253495047396</v>
+        <v>0.99849712388517564</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>86667</v>
+        <v>86668</v>
       </c>
       <c r="U33" s="8">
-        <v>593531</v>
+        <v>593532</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>0.99040847418314337</v>
+        <v>0.9904101428549974</v>
       </c>
       <c r="W33" s="9">
         <v>608923</v>
@@ -6373,14 +6373,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>71279</v>
+        <v>71280</v>
       </c>
       <c r="AY33" s="22">
-        <v>611826</v>
+        <v>611827</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>0.9780061862097077</v>
+        <v>0.97800778471350813</v>
       </c>
       <c r="BA33" s="9">
         <v>617039</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>71310</v>
+        <v>71312</v>
       </c>
       <c r="BD33" s="8">
-        <v>617614</v>
+        <v>617616</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0009318697845679</v>
+        <v>1.0009351110707752</v>
       </c>
       <c r="BF33" s="9">
         <v>1025594</v>
@@ -6407,14 +6407,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>171347</v>
+        <v>171349</v>
       </c>
       <c r="BI33" s="8">
-        <v>1028387</v>
+        <v>1028389</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>1.0027232998632987</v>
+        <v>1.0027252499527104</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6832,14 +6832,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>170299</v>
+        <v>170303</v>
       </c>
       <c r="F36" s="22">
-        <v>777390</v>
+        <v>777394</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.96672142421012974</v>
+        <v>0.96672639840030039</v>
       </c>
       <c r="H36" s="9">
         <v>814447</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="2"/>
-        <v>192039</v>
+        <v>192043</v>
       </c>
       <c r="K36" s="22">
-        <v>789169</v>
+        <v>789173</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="3"/>
-        <v>0.96896298961135596</v>
+        <v>0.96896790091927409</v>
       </c>
       <c r="M36" s="4">
         <v>1485608</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="4"/>
-        <v>325457</v>
+        <v>325465</v>
       </c>
       <c r="P36" s="8">
-        <v>1435399</v>
+        <v>1435407</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="5"/>
-        <v>0.96620306298835223</v>
+        <v>0.96620844798897154</v>
       </c>
       <c r="R36" s="9">
         <v>815623</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="6"/>
-        <v>178513</v>
+        <v>178518</v>
       </c>
       <c r="U36" s="8">
-        <v>787775</v>
+        <v>787780</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="7"/>
-        <v>0.96585677451469609</v>
+        <v>0.96586290479792747</v>
       </c>
       <c r="W36" s="9">
         <v>826349</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="8"/>
-        <v>192829</v>
+        <v>192833</v>
       </c>
       <c r="Z36" s="22">
-        <v>797817</v>
+        <v>797821</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="9"/>
-        <v>0.96547221573451414</v>
+        <v>0.96547705630429759</v>
       </c>
       <c r="AB36" s="9">
         <v>1500292</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="10"/>
-        <v>350452</v>
+        <v>350460</v>
       </c>
       <c r="AE36" s="8">
-        <v>1453924</v>
+        <v>1453932</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="11"/>
-        <v>0.96909401636481429</v>
+        <v>0.96909934866012748</v>
       </c>
       <c r="AG36" s="9">
         <v>833041</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>198252</v>
+        <v>198257</v>
       </c>
       <c r="AJ36" s="22">
-        <v>803848</v>
+        <v>803853</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="13"/>
-        <v>0.964956106602196</v>
+        <v>0.96496210870773469</v>
       </c>
       <c r="AL36" s="9">
         <v>845911</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="14"/>
-        <v>169662</v>
+        <v>169668</v>
       </c>
       <c r="AO36" s="22">
-        <v>816471</v>
+        <v>816477</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="15"/>
-        <v>0.96519728434788055</v>
+        <v>0.96520437729264663</v>
       </c>
       <c r="AQ36" s="15">
         <v>1519147</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="16"/>
-        <v>287941</v>
+        <v>287949</v>
       </c>
       <c r="AT36" s="8">
-        <v>1474567</v>
+        <v>1474575</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="17"/>
-        <v>0.97065458444771968</v>
+        <v>0.970659850560874</v>
       </c>
       <c r="AV36" s="9">
         <v>864672</v>
@@ -6985,14 +6985,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="18"/>
-        <v>160506</v>
+        <v>160512</v>
       </c>
       <c r="AY36" s="22">
-        <v>819060</v>
+        <v>819066</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="19"/>
-        <v>0.94724936160763851</v>
+        <v>0.94725630065504607</v>
       </c>
       <c r="BA36" s="9">
         <v>838532</v>
@@ -7002,14 +7002,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="20"/>
-        <v>161121</v>
+        <v>161129</v>
       </c>
       <c r="BD36" s="8">
-        <v>830663</v>
+        <v>830671</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="21"/>
-        <v>0.99061574275042574</v>
+        <v>0.99062528323307875</v>
       </c>
       <c r="BF36" s="9">
         <v>1502094</v>
@@ -7019,14 +7019,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="22"/>
-        <v>388504</v>
+        <v>388510</v>
       </c>
       <c r="BI36" s="8">
-        <v>1495223</v>
+        <v>1495229</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="23"/>
-        <v>0.995425719029568</v>
+        <v>0.9954297134533524</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7044,14 +7044,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>111292</v>
+        <v>111294</v>
       </c>
       <c r="F37" s="22">
-        <v>621140</v>
+        <v>621142</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.95466442885971747</v>
+        <v>0.95466750277036194</v>
       </c>
       <c r="H37" s="9">
         <v>656039</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="2"/>
-        <v>125869</v>
+        <v>125871</v>
       </c>
       <c r="K37" s="22">
-        <v>626363</v>
+        <v>626365</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="3"/>
-        <v>0.95476488440473817</v>
+        <v>0.95476793300398299</v>
       </c>
       <c r="M37" s="4">
         <v>844882</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="4"/>
-        <v>156055</v>
+        <v>156062</v>
       </c>
       <c r="P37" s="8">
-        <v>804133</v>
+        <v>804140</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="5"/>
-        <v>0.9517695962276389</v>
+        <v>0.95177788140829134</v>
       </c>
       <c r="R37" s="9">
         <v>664863</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="6"/>
-        <v>120164</v>
+        <v>120168</v>
       </c>
       <c r="U37" s="8">
-        <v>632162</v>
+        <v>632166</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="7"/>
-        <v>0.9508154311489736</v>
+        <v>0.95082144742601105</v>
       </c>
       <c r="W37" s="9">
         <v>670009</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="8"/>
-        <v>127257</v>
+        <v>127263</v>
       </c>
       <c r="Z37" s="22">
-        <v>638027</v>
+        <v>638033</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="9"/>
-        <v>0.95226631284057384</v>
+        <v>0.95227526794416195</v>
       </c>
       <c r="AB37" s="9">
         <v>858143</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="10"/>
-        <v>183057</v>
+        <v>183066</v>
       </c>
       <c r="AE37" s="8">
-        <v>818674</v>
+        <v>818683</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="11"/>
-        <v>0.95400650008215415</v>
+        <v>0.95401698784468325</v>
       </c>
       <c r="AG37" s="9">
         <v>675943</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>129774</v>
+        <v>129778</v>
       </c>
       <c r="AJ37" s="22">
-        <v>644481</v>
+        <v>644485</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="13"/>
-        <v>0.95345465520021655</v>
+        <v>0.95346057285895414</v>
       </c>
       <c r="AL37" s="9">
         <v>678429</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="14"/>
-        <v>111968</v>
+        <v>111972</v>
       </c>
       <c r="AO37" s="22">
-        <v>650682</v>
+        <v>650686</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="15"/>
-        <v>0.9591010997466205</v>
+        <v>0.95910699572099656</v>
       </c>
       <c r="AQ37" s="15">
         <v>865622</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="16"/>
-        <v>140851</v>
+        <v>140858</v>
       </c>
       <c r="AT37" s="8">
-        <v>832592</v>
+        <v>832599</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="17"/>
-        <v>0.96184246703526477</v>
+        <v>0.96185055370589012</v>
       </c>
       <c r="AV37" s="9">
         <v>690116</v>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="18"/>
-        <v>115288</v>
+        <v>115292</v>
       </c>
       <c r="AY37" s="22">
-        <v>658576</v>
+        <v>658580</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="19"/>
-        <v>0.95429753838485121</v>
+        <v>0.95430333451187921</v>
       </c>
       <c r="BA37" s="9">
         <v>673244</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="20"/>
-        <v>114868</v>
+        <v>114873</v>
       </c>
       <c r="BD37" s="8">
-        <v>664887</v>
+        <v>664892</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="21"/>
-        <v>0.98758696698373849</v>
+        <v>0.98759439371164093</v>
       </c>
       <c r="BF37" s="9">
         <v>856336</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="22"/>
-        <v>202730</v>
+        <v>202735</v>
       </c>
       <c r="BI37" s="8">
-        <v>846545</v>
+        <v>846550</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="23"/>
-        <v>0.98856640384148275</v>
+        <v>0.98857224267110111</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="14"/>
-        <v>6177</v>
+        <v>6178</v>
       </c>
       <c r="AO38" s="22">
-        <v>22402</v>
+        <v>22403</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="15"/>
-        <v>0.88412660825637379</v>
+        <v>0.88416607467045549</v>
       </c>
       <c r="AQ38" s="15">
         <v>38074</v>
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>50307</v>
+        <v>50310</v>
       </c>
       <c r="F40" s="22">
-        <v>260475</v>
+        <v>260478</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.9524497310579606</v>
+        <v>0.95246070082163525</v>
       </c>
       <c r="H40" s="9">
         <v>275367</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="2"/>
-        <v>57017</v>
+        <v>57021</v>
       </c>
       <c r="K40" s="22">
-        <v>262129</v>
+        <v>262133</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="3"/>
-        <v>0.95192597515315924</v>
+        <v>0.95194050122200558</v>
       </c>
       <c r="M40" s="4">
         <v>339208</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="4"/>
-        <v>69729</v>
+        <v>69737</v>
       </c>
       <c r="P40" s="8">
-        <v>323329</v>
+        <v>323337</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="5"/>
-        <v>0.95318801443362189</v>
+        <v>0.95321159878304762</v>
       </c>
       <c r="R40" s="9">
         <v>277547</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="6"/>
-        <v>54041</v>
+        <v>54044</v>
       </c>
       <c r="U40" s="8">
-        <v>264303</v>
+        <v>264306</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="7"/>
-        <v>0.95228195584891928</v>
+        <v>0.95229276482901992</v>
       </c>
       <c r="W40" s="9">
         <v>278758</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="8"/>
-        <v>62703</v>
+        <v>62707</v>
       </c>
       <c r="Z40" s="22">
-        <v>266748</v>
+        <v>266752</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="9"/>
-        <v>0.95691603469676212</v>
+        <v>0.9569303840607265</v>
       </c>
       <c r="AB40" s="9">
         <v>343140</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="10"/>
-        <v>81810</v>
+        <v>81819</v>
       </c>
       <c r="AE40" s="8">
-        <v>328067</v>
+        <v>328076</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="11"/>
-        <v>0.95607332284198865</v>
+        <v>0.95609955120359036</v>
       </c>
       <c r="AG40" s="9">
         <v>282101</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>62428</v>
+        <v>62432</v>
       </c>
       <c r="AJ40" s="22">
-        <v>268626</v>
+        <v>268630</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="13"/>
-        <v>0.95223341994533872</v>
+        <v>0.9522475992640933</v>
       </c>
       <c r="AL40" s="9">
         <v>282756</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="14"/>
-        <v>55738</v>
+        <v>55744</v>
       </c>
       <c r="AO40" s="22">
-        <v>270853</v>
+        <v>270859</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="15"/>
-        <v>0.95790363422880509</v>
+        <v>0.95792485393767068</v>
       </c>
       <c r="AQ40" s="15">
         <v>343988</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="16"/>
-        <v>66697</v>
+        <v>66708</v>
       </c>
       <c r="AT40" s="8">
-        <v>332178</v>
+        <v>332189</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="17"/>
-        <v>0.96566740700256981</v>
+        <v>0.96569938486226259</v>
       </c>
       <c r="AV40" s="9">
         <v>285285</v>
@@ -7833,14 +7833,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="18"/>
-        <v>56525</v>
+        <v>56534</v>
       </c>
       <c r="AY40" s="22">
-        <v>273377</v>
+        <v>273386</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="19"/>
-        <v>0.95825928457507403</v>
+        <v>0.9582908319750425</v>
       </c>
       <c r="BA40" s="9">
         <v>276279</v>
@@ -7850,14 +7850,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="20"/>
-        <v>55347</v>
+        <v>55351</v>
       </c>
       <c r="BD40" s="8">
-        <v>275300</v>
+        <v>275304</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="21"/>
-        <v>0.99645648058665337</v>
+        <v>0.99647095870478752</v>
       </c>
       <c r="BF40" s="9">
         <v>339189</v>
@@ -7867,14 +7867,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="22"/>
-        <v>95141</v>
+        <v>95146</v>
       </c>
       <c r="BI40" s="8">
-        <v>336915</v>
+        <v>336920</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="23"/>
-        <v>0.99329577315302087</v>
+        <v>0.99331051419709959</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>119530</v>
+        <v>119539</v>
       </c>
       <c r="F41" s="22">
-        <v>840978</v>
+        <v>840987</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.96366178138858016</v>
+        <v>0.96367209432902867</v>
       </c>
       <c r="H41" s="9">
         <v>878008</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="2"/>
-        <v>149518</v>
+        <v>149527</v>
       </c>
       <c r="K41" s="22">
-        <v>848042</v>
+        <v>848051</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="3"/>
-        <v>0.96587047042851548</v>
+        <v>0.96588072090459309</v>
       </c>
       <c r="M41" s="4">
         <v>999035</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="4"/>
-        <v>161308</v>
+        <v>161321</v>
       </c>
       <c r="P41" s="8">
-        <v>960795</v>
+        <v>960808</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="5"/>
-        <v>0.96172306275555908</v>
+        <v>0.96173607531267669</v>
       </c>
       <c r="R41" s="9">
         <v>889467</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="6"/>
-        <v>146336</v>
+        <v>146347</v>
       </c>
       <c r="U41" s="8">
-        <v>857030</v>
+        <v>857041</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="7"/>
-        <v>0.96353209281513541</v>
+        <v>0.96354445977197578</v>
       </c>
       <c r="W41" s="9">
         <v>894020</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="8"/>
-        <v>153057</v>
+        <v>153066</v>
       </c>
       <c r="Z41" s="22">
-        <v>862433</v>
+        <v>862442</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="9"/>
-        <v>0.9646685756470772</v>
+        <v>0.96467864253596114</v>
       </c>
       <c r="AB41" s="9">
         <v>1012178</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="10"/>
-        <v>189517</v>
+        <v>189532</v>
       </c>
       <c r="AE41" s="8">
-        <v>976721</v>
+        <v>976736</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="11"/>
-        <v>0.96496960020865896</v>
+        <v>0.96498441973644955</v>
       </c>
       <c r="AG41" s="9">
         <v>904846</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>152734</v>
+        <v>152746</v>
       </c>
       <c r="AJ41" s="22">
-        <v>872489</v>
+        <v>872501</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="13"/>
-        <v>0.96424032376780133</v>
+        <v>0.9642535856930351</v>
       </c>
       <c r="AL41" s="9">
         <v>910192</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="14"/>
-        <v>133995</v>
+        <v>134008</v>
       </c>
       <c r="AO41" s="22">
-        <v>878401</v>
+        <v>878414</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="15"/>
-        <v>0.96507220454585407</v>
+        <v>0.96508648724664681</v>
       </c>
       <c r="AQ41" s="15">
         <v>1025826</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="16"/>
-        <v>163966</v>
+        <v>163982</v>
       </c>
       <c r="AT41" s="8">
-        <v>991930</v>
+        <v>991946</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="17"/>
-        <v>0.96695735924026105</v>
+        <v>0.96697295642730829</v>
       </c>
       <c r="AV41" s="9">
         <v>923071</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="18"/>
-        <v>137857</v>
+        <v>137872</v>
       </c>
       <c r="AY41" s="22">
-        <v>890396</v>
+        <v>890411</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="19"/>
-        <v>0.96460185619524397</v>
+        <v>0.96461810629951539</v>
       </c>
       <c r="BA41" s="9">
         <v>907892</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="20"/>
-        <v>135544</v>
+        <v>135554</v>
       </c>
       <c r="BD41" s="8">
-        <v>897231</v>
+        <v>897241</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="21"/>
-        <v>0.9882574138774215</v>
+        <v>0.98826842840337836</v>
       </c>
       <c r="BF41" s="9">
         <v>1023930</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="22"/>
-        <v>214806</v>
+        <v>214816</v>
       </c>
       <c r="BI41" s="8">
-        <v>1010521</v>
+        <v>1010531</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="23"/>
-        <v>0.98690437822898047</v>
+        <v>0.9869141445215982</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F43" s="22">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="24"/>
-        <v>0.94815256257449343</v>
+        <v>0.94845053635280097</v>
       </c>
       <c r="H43" s="9">
         <v>3369</v>
@@ -8333,14 +8333,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="K43" s="22">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="3"/>
-        <v>0.9581478183437222</v>
+        <v>0.95844464232710003</v>
       </c>
       <c r="M43" s="4">
         <v>4189</v>
@@ -8350,14 +8350,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="4"/>
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="P43" s="8">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="5"/>
-        <v>0.96419193124850799</v>
+        <v>0.96443065170685127</v>
       </c>
       <c r="R43" s="9">
         <v>3398</v>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="6"/>
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="U43" s="8">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="7"/>
-        <v>0.96615656268393169</v>
+        <v>0.96645085344320192</v>
       </c>
       <c r="W43" s="9">
         <v>3433</v>
@@ -8384,14 +8384,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="8"/>
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="Z43" s="22">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="9"/>
-        <v>0.97261870084474222</v>
+        <v>0.97290999126128752</v>
       </c>
       <c r="AB43" s="9">
         <v>4306</v>
@@ -8401,14 +8401,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="10"/>
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="AE43" s="8">
-        <v>4182</v>
+        <v>4183</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="11"/>
-        <v>0.97120297259637711</v>
+        <v>0.97143520668834182</v>
       </c>
       <c r="AG43" s="9">
         <v>3505</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="12"/>
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="AJ43" s="22">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="13"/>
-        <v>0.95263908701854494</v>
+        <v>0.95292439372325255</v>
       </c>
       <c r="AL43" s="9">
         <v>3511</v>
@@ -8435,14 +8435,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="14"/>
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AO43" s="22">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="15"/>
-        <v>0.95984050128168608</v>
+        <v>0.96012532042153231</v>
       </c>
       <c r="AQ43" s="15">
         <v>4405</v>
@@ -8452,14 +8452,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="16"/>
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="AT43" s="8">
-        <v>4262</v>
+        <v>4263</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="17"/>
-        <v>0.96753688989784337</v>
+        <v>0.96776390465380246</v>
       </c>
       <c r="AV43" s="9">
         <v>3534</v>
@@ -8469,14 +8469,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="18"/>
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="AY43" s="22">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="19"/>
-        <v>0.96151669496321446</v>
+        <v>0.96179966044142617</v>
       </c>
       <c r="BA43" s="9">
         <v>3464</v>
@@ -8486,14 +8486,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="20"/>
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="BD43" s="8">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="21"/>
-        <v>0.99682448036951499</v>
+        <v>0.99711316397228633</v>
       </c>
       <c r="BF43" s="9">
         <v>4361</v>
@@ -8503,14 +8503,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="22"/>
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="BI43" s="8">
-        <v>4334</v>
+        <v>4335</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="23"/>
-        <v>0.99380875945883973</v>
+        <v>0.99403806466406786</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>67405</v>
+        <v>67406</v>
       </c>
       <c r="F44" s="22">
-        <v>304563</v>
+        <v>304564</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.89538640646543999</v>
+        <v>0.89538934637083378</v>
       </c>
       <c r="H44" s="9">
         <v>343940</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
-        <v>78209</v>
+        <v>78210</v>
       </c>
       <c r="K44" s="22">
-        <v>307775</v>
+        <v>307776</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="3"/>
-        <v>0.8948508460778043</v>
+        <v>0.89485375356166774</v>
       </c>
       <c r="M44" s="4">
         <v>415294</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="4"/>
-        <v>88839</v>
+        <v>88840</v>
       </c>
       <c r="P44" s="8">
-        <v>373546</v>
+        <v>373547</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="5"/>
-        <v>0.89947362591320845</v>
+        <v>0.89947603384590191</v>
       </c>
       <c r="R44" s="9">
         <v>349377</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="6"/>
-        <v>76588</v>
+        <v>76589</v>
       </c>
       <c r="U44" s="8">
-        <v>311989</v>
+        <v>311990</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="7"/>
-        <v>0.89298665911035935</v>
+        <v>0.89298952134799947</v>
       </c>
       <c r="W44" s="9">
         <v>352323</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="8"/>
-        <v>77413</v>
+        <v>77414</v>
       </c>
       <c r="Z44" s="22">
-        <v>315074</v>
+        <v>315075</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="9"/>
-        <v>0.8942759910650171</v>
+        <v>0.89427882936964087</v>
       </c>
       <c r="AB44" s="9">
         <v>424236</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="10"/>
-        <v>99658</v>
+        <v>99659</v>
       </c>
       <c r="AE44" s="8">
-        <v>382540</v>
+        <v>382541</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="11"/>
-        <v>0.90171508311411575</v>
+        <v>0.90171744029266732</v>
       </c>
       <c r="AG44" s="9">
         <v>358309</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>80230</v>
+        <v>80231</v>
       </c>
       <c r="AJ44" s="22">
-        <v>319570</v>
+        <v>319571</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="13"/>
-        <v>0.89188382094784113</v>
+        <v>0.89188661183503626</v>
       </c>
       <c r="AL44" s="9">
         <v>359722</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="14"/>
-        <v>71149</v>
+        <v>71150</v>
       </c>
       <c r="AO44" s="22">
-        <v>323331</v>
+        <v>323332</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="15"/>
-        <v>0.8988357676205514</v>
+        <v>0.89883854754504866</v>
       </c>
       <c r="AQ44" s="15">
         <v>432157</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="16"/>
-        <v>82582</v>
+        <v>82583</v>
       </c>
       <c r="AT44" s="8">
-        <v>390814</v>
+        <v>390815</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="17"/>
-        <v>0.9043333788414859</v>
+        <v>0.90433569281534254</v>
       </c>
       <c r="AV44" s="9">
         <v>367733</v>
@@ -8681,14 +8681,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="18"/>
-        <v>71253</v>
+        <v>71254</v>
       </c>
       <c r="AY44" s="22">
-        <v>327466</v>
+        <v>327467</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="19"/>
-        <v>0.89049935687033799</v>
+        <v>0.89050207623465938</v>
       </c>
       <c r="BA44" s="9">
         <v>337773</v>
@@ -8698,14 +8698,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="20"/>
-        <v>71566</v>
+        <v>71567</v>
       </c>
       <c r="BD44" s="8">
-        <v>331168</v>
+        <v>331169</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="21"/>
-        <v>0.98044544709020554</v>
+        <v>0.9804484076583978</v>
       </c>
       <c r="BF44" s="9">
         <v>408499</v>
@@ -8715,14 +8715,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="22"/>
-        <v>111946</v>
+        <v>111948</v>
       </c>
       <c r="BI44" s="8">
-        <v>399296</v>
+        <v>399298</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="23"/>
-        <v>0.97747118108000264</v>
+        <v>0.97747607705282025</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>45809</v>
+        <v>45812</v>
       </c>
       <c r="F45" s="22">
-        <v>235579</v>
+        <v>235582</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.94166813232496038</v>
+        <v>0.94168012407463664</v>
       </c>
       <c r="H45" s="9">
         <v>249985</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="2"/>
-        <v>49313</v>
+        <v>49317</v>
       </c>
       <c r="K45" s="22">
-        <v>237259</v>
+        <v>237263</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="3"/>
-        <v>0.94909294557673463</v>
+        <v>0.94910894653679223</v>
       </c>
       <c r="M45" s="4">
         <v>300587</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="4"/>
-        <v>59180</v>
+        <v>59184</v>
       </c>
       <c r="P45" s="8">
-        <v>288726</v>
+        <v>288730</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="5"/>
-        <v>0.96054054233882369</v>
+        <v>0.96055384963421575</v>
       </c>
       <c r="R45" s="9">
         <v>247712</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="6"/>
-        <v>49704</v>
+        <v>49708</v>
       </c>
       <c r="U45" s="8">
-        <v>238338</v>
+        <v>238342</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="7"/>
-        <v>0.96215766696809202</v>
+        <v>0.96217381475261599</v>
       </c>
       <c r="W45" s="9">
         <v>250023</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="8"/>
-        <v>53058</v>
+        <v>53062</v>
       </c>
       <c r="Z45" s="22">
-        <v>240170</v>
+        <v>240174</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="9"/>
-        <v>0.96059162557044753</v>
+        <v>0.96060762409858291</v>
       </c>
       <c r="AB45" s="9">
         <v>306096</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="10"/>
-        <v>69243</v>
+        <v>69246</v>
       </c>
       <c r="AE45" s="8">
-        <v>293557</v>
+        <v>293560</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="11"/>
-        <v>0.95903572735351006</v>
+        <v>0.9590455282003032</v>
       </c>
       <c r="AG45" s="9">
         <v>252706</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>51721</v>
+        <v>51724</v>
       </c>
       <c r="AJ45" s="22">
-        <v>243559</v>
+        <v>243562</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="13"/>
-        <v>0.96380378780084364</v>
+        <v>0.96381565930369684</v>
       </c>
       <c r="AL45" s="9">
         <v>254538</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="14"/>
-        <v>44679</v>
+        <v>44682</v>
       </c>
       <c r="AO45" s="22">
-        <v>245892</v>
+        <v>245895</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="15"/>
-        <v>0.96603257666831677</v>
+        <v>0.96604436272776562</v>
       </c>
       <c r="AQ45" s="15">
         <v>310997</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="16"/>
-        <v>57338</v>
+        <v>57341</v>
       </c>
       <c r="AT45" s="8">
-        <v>299350</v>
+        <v>299353</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="17"/>
-        <v>0.96254947796924084</v>
+        <v>0.96255912436454372</v>
       </c>
       <c r="AV45" s="9">
         <v>259359</v>
@@ -8893,14 +8893,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="18"/>
-        <v>47793</v>
+        <v>47796</v>
       </c>
       <c r="AY45" s="22">
-        <v>248473</v>
+        <v>248476</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="19"/>
-        <v>0.95802729035815226</v>
+        <v>0.95803885733674177</v>
       </c>
       <c r="BA45" s="9">
         <v>254394</v>
@@ -8910,14 +8910,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="20"/>
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="BD45" s="8">
-        <v>250274</v>
+        <v>250277</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="21"/>
-        <v>0.98380464948072677</v>
+        <v>0.9838164422116874</v>
       </c>
       <c r="BF45" s="9">
         <v>309142</v>
@@ -8927,14 +8927,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="22"/>
-        <v>80316</v>
+        <v>80319</v>
       </c>
       <c r="BI45" s="8">
-        <v>304210</v>
+        <v>304213</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="23"/>
-        <v>0.98404616648659837</v>
+        <v>0.98405587076489121</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9376,15 +9376,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ref="E48" si="25">F48-D48</f>
-        <v>1278073</v>
+        <v>1278120</v>
       </c>
       <c r="F48" s="12">
         <f>SUM(F10:F47)</f>
-        <v>7088335</v>
+        <v>7088382</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" ref="G48" si="26">F48/C48</f>
-        <v>0.9583230301802057</v>
+        <v>0.95832938444850968</v>
       </c>
       <c r="H48" s="11">
         <f>SUM(H10:H47)</f>
@@ -9396,15 +9396,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" ref="J48" si="27">K48-I48</f>
-        <v>1509312</v>
+        <v>1509363</v>
       </c>
       <c r="K48" s="12">
         <f>SUM(K10:K47)</f>
-        <v>7194445</v>
+        <v>7194496</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" ref="L48" si="28">K48/H48</f>
-        <v>0.95982499019422107</v>
+        <v>0.95983179420405096</v>
       </c>
       <c r="M48" s="11">
         <f>SUM(M10:M47)</f>
@@ -9416,15 +9416,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2205408</v>
+        <v>2205491</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>11346745</v>
+        <v>11346828</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.9582424254963916</v>
+        <v>0.95824943491815229</v>
       </c>
       <c r="R48" s="11">
         <f>SUM(R10:R47)</f>
@@ -9436,15 +9436,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>1416009</v>
+        <v>1416070</v>
       </c>
       <c r="U48" s="12">
         <f>SUM(U10:U47)</f>
-        <v>7214394</v>
+        <v>7214455</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.95638225680364386</v>
+        <v>0.95639034332035822</v>
       </c>
       <c r="W48" s="11">
         <f>SUM(W10:W47)</f>
@@ -9456,15 +9456,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>1498849</v>
+        <v>1498910</v>
       </c>
       <c r="Z48" s="12">
         <f>SUM(Z10:Z47)</f>
-        <v>7308866</v>
+        <v>7308927</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.95777659664246562</v>
+        <v>0.95778459027272167</v>
       </c>
       <c r="AB48" s="11">
         <f>SUM(AB10:AB47)</f>
@@ -9476,15 +9476,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2513110</v>
+        <v>2513200</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>11559746</v>
+        <v>11559836</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.96007814344048736</v>
+        <v>0.96008561826155259</v>
       </c>
       <c r="AG48" s="11">
         <f>SUM(AG10:AG47)</f>
@@ -9496,15 +9496,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>1514820</v>
+        <v>1514888</v>
       </c>
       <c r="AJ48" s="12">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7365112</v>
+        <v>7365180</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.9556931063718912</v>
+        <v>0.9557019300165599</v>
       </c>
       <c r="AL48" s="11">
         <f>SUM(AL10:AL47)</f>
@@ -9516,15 +9516,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>1322656</v>
+        <v>1322734</v>
       </c>
       <c r="AO48" s="12">
         <f>SUM(AO10:AO47)</f>
-        <v>7467869</v>
+        <v>7467947</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.95751374911545739</v>
+        <v>0.95752375010401669</v>
       </c>
       <c r="AQ48" s="11">
         <f>SUM(AQ10:AQ47)</f>
@@ -9536,15 +9536,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>1994706</v>
+        <v>1994812</v>
       </c>
       <c r="AT48" s="12">
         <f>SUM(AT10:AT47)</f>
-        <v>11757375</v>
+        <v>11757481</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.96133554413560274</v>
+        <v>0.96134421116950097</v>
       </c>
       <c r="AV48" s="11">
         <f>SUM(AV10:AV47)</f>
@@ -9556,15 +9556,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>1323133</v>
+        <v>1323221</v>
       </c>
       <c r="AY48" s="12">
         <f>SUM(AY10:AY47)</f>
-        <v>7529817</v>
+        <v>7529905</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.94283123449158313</v>
+        <v>0.94284225323860382</v>
       </c>
       <c r="BA48" s="11">
         <f>SUM(BA10:BA47)</f>
@@ -9576,15 +9576,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>1344785</v>
+        <v>1344866</v>
       </c>
       <c r="BD48" s="12">
         <f>SUM(BD10:BD47)</f>
-        <v>7633265</v>
+        <v>7633346</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.98857896157354863</v>
+        <v>0.98858945182849034</v>
       </c>
       <c r="BF48" s="11">
         <f>SUM(BF10:BF47)</f>
@@ -9596,15 +9596,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>2842114</v>
+        <v>2842212</v>
       </c>
       <c r="BI48" s="12">
         <f>SUM(BI10:BI47)</f>
-        <v>11980002</v>
+        <v>11980100</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.9927564424951727</v>
+        <v>0.99276456353984077</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
